--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\TN\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3CDACEF-2625-4F19-8B79-9F973DDBF1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6968E3B7-53B9-42D5-AE37-F2132A118891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12195" yWindow="225" windowWidth="16605" windowHeight="17055" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -533,12 +533,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -546,15 +546,15 @@
         <v>40</v>
       </c>
       <c r="C1" s="5">
-        <v>45237</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,55 +562,55 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -627,13 +627,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -641,7 +641,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -665,23 +665,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -705,7 +705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -721,7 +721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -754,7 +754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
@@ -845,13 +845,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -923,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -939,7 +939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\TN\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6968E3B7-53B9-42D5-AE37-F2132A118891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D371034E-7063-4409-A6C3-BC62F369EC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12195" yWindow="225" windowWidth="16605" windowHeight="17055" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="485" yWindow="455" windowWidth="14400" windowHeight="7455" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId2"/>
-    <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId3"/>
+    <sheet name="RQSD-RQSD" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
   <si>
     <t>Source:</t>
   </si>
@@ -154,6 +155,99 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>DEFAULT</t>
   </si>
   <si>
     <t>Tennessee</t>
@@ -232,7 +326,18 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -533,28 +638,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="84.5703125" customWidth="1"/>
+    <col min="2" max="2" width="84.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C1" s="5">
-        <v>45302</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,55 +667,55 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -622,18 +727,2517 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20170993-D933-4301-A5EB-F72DC832967D}">
+  <dimension ref="A1:AF25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <f>B2</f>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:AC14" si="0">C2</f>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" ref="AD14:AF14" si="1">AD2</f>
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AE19">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AE20">
+        <v>1</v>
+      </c>
+      <c r="AF20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21">
+        <v>1</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AE21">
+        <v>1</v>
+      </c>
+      <c r="AF21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
+        <v>1</v>
+      </c>
+      <c r="AF22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.75">
+      <c r="A25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+      <c r="AB25">
+        <v>1</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A5:XFD6">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.40625" customWidth="1"/>
+    <col min="2" max="2" width="28.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -641,196 +3245,219 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A2,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A3,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A4,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A5,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A6,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A7,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A8,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A9,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A10,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
       <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A11,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B11)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>9</v>
       </c>
       <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A12,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A13,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
-        <f>B2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A14,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A15,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B15)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>27</v>
       </c>
       <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A16,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A17,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>29</v>
       </c>
       <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A18,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B18)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>33</v>
       </c>
       <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A19,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B19)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>34</v>
       </c>
       <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A20,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B20)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>35</v>
       </c>
       <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A21,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B21)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>36</v>
       </c>
       <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A22,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B22)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>37</v>
       </c>
       <c r="B23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A23,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B23)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A24,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B24)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B25">
+        <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A25,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B25)</f>
         <v>1</v>
       </c>
     </row>
@@ -839,19 +3466,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.40625" customWidth="1"/>
+    <col min="2" max="2" width="28.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,7 +3486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -867,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -875,7 +3502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -883,7 +3510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -891,7 +3518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -899,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -907,7 +3534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -923,7 +3550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -931,7 +3558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -939,7 +3566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -947,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -955,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -964,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -972,7 +3599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -980,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -988,7 +3615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -996,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1004,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +3639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1020,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1028,7 +3655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1036,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1044,7 +3671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\TN\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D371034E-7063-4409-A6C3-BC62F369EC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{924A6B9C-E021-4B22-B326-ABC5ABAE6AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="485" yWindow="455" windowWidth="14400" windowHeight="7455" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="3900" windowWidth="28785" windowHeight="13680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="75">
   <si>
     <t>Source:</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
   </si>
   <si>
-    <t>see notes</t>
-  </si>
-  <si>
     <t>crude oil</t>
   </si>
   <si>
@@ -248,6 +245,18 @@
   </si>
   <si>
     <t>DEFAULT</t>
+  </si>
+  <si>
+    <t>Database of State Incentives for Renewables and Efficiency</t>
+  </si>
+  <si>
+    <t>https://www.dsireusa.org/</t>
+  </si>
+  <si>
+    <t>DSIRE</t>
+  </si>
+  <si>
+    <t>Feb 14 2023</t>
   </si>
   <si>
     <t>Tennessee</t>
@@ -326,7 +335,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -334,6 +343,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -638,84 +657,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1" s="5">
-        <v>45316</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -729,110 +760,110 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20170993-D933-4301-A5EB-F72DC832967D}">
   <dimension ref="A1:AF25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>48</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>49</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>50</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>51</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>52</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>54</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>55</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>56</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>57</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>58</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>59</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>60</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>61</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>62</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>63</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>64</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>66</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>67</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>68</v>
       </c>
-      <c r="AF1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -930,108 +961,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
       <c r="B4">
         <v>0</v>
       </c>
@@ -1126,7 +1157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1194,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1224,7 +1255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1283,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>1</v>
@@ -1292,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -1322,7 +1353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1420,7 +1451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1518,7 +1549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1616,7 +1647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1714,7 +1745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1812,7 +1843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1910,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -2008,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2137,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -2235,206 +2266,206 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>27</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>28</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
       <c r="B18">
         <v>1</v>
       </c>
@@ -2529,695 +2560,820 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f>B19</f>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:AF22" si="2">C19</f>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>33</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19">
-        <v>1</v>
-      </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-      <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>1</v>
-      </c>
-      <c r="Z19">
-        <v>1</v>
-      </c>
-      <c r="AA19">
-        <v>1</v>
-      </c>
-      <c r="AB19">
-        <v>1</v>
-      </c>
-      <c r="AC19">
-        <v>1</v>
-      </c>
-      <c r="AD19">
-        <v>1</v>
-      </c>
-      <c r="AE19">
-        <v>1</v>
-      </c>
-      <c r="AF19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f t="shared" ref="C20:R22" si="3">B20</f>
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>34</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-      <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="Q20">
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
-      </c>
-      <c r="S20">
-        <v>1</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
-      </c>
-      <c r="U20">
-        <v>1</v>
-      </c>
-      <c r="V20">
-        <v>1</v>
-      </c>
-      <c r="W20">
-        <v>1</v>
-      </c>
-      <c r="X20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
-      <c r="Z20">
-        <v>1</v>
-      </c>
-      <c r="AA20">
-        <v>1</v>
-      </c>
-      <c r="AB20">
-        <v>1</v>
-      </c>
-      <c r="AC20">
-        <v>1</v>
-      </c>
-      <c r="AD20">
-        <v>1</v>
-      </c>
-      <c r="AE20">
-        <v>1</v>
-      </c>
-      <c r="AF20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>35</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>1</v>
-      </c>
-      <c r="S21">
-        <v>1</v>
-      </c>
-      <c r="T21">
-        <v>1</v>
-      </c>
-      <c r="U21">
-        <v>1</v>
-      </c>
-      <c r="V21">
-        <v>1</v>
-      </c>
-      <c r="W21">
-        <v>1</v>
-      </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="Y21">
-        <v>1</v>
-      </c>
-      <c r="Z21">
-        <v>1</v>
-      </c>
-      <c r="AA21">
-        <v>1</v>
-      </c>
-      <c r="AB21">
-        <v>1</v>
-      </c>
-      <c r="AC21">
-        <v>1</v>
-      </c>
-      <c r="AD21">
-        <v>1</v>
-      </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AF21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A22" t="s">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>36</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22">
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-      <c r="S22">
-        <v>1</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-      <c r="W22">
-        <v>1</v>
-      </c>
-      <c r="X22">
-        <v>1</v>
-      </c>
-      <c r="Y22">
-        <v>1</v>
-      </c>
-      <c r="Z22">
-        <v>1</v>
-      </c>
-      <c r="AA22">
-        <v>1</v>
-      </c>
-      <c r="AB22">
-        <v>1</v>
-      </c>
-      <c r="AC22">
-        <v>1</v>
-      </c>
-      <c r="AD22">
-        <v>1</v>
-      </c>
-      <c r="AE22">
-        <v>1</v>
-      </c>
-      <c r="AF22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A23" t="s">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-      <c r="P23">
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
-      </c>
-      <c r="S23">
-        <v>1</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-      <c r="W23">
-        <v>1</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>1</v>
-      </c>
-      <c r="Z23">
-        <v>1</v>
-      </c>
-      <c r="AA23">
-        <v>1</v>
-      </c>
-      <c r="AB23">
-        <v>1</v>
-      </c>
-      <c r="AC23">
-        <v>1</v>
-      </c>
-      <c r="AD23">
-        <v>1</v>
-      </c>
-      <c r="AE23">
-        <v>1</v>
-      </c>
-      <c r="AF23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A24" s="4" t="s">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <v>1</v>
-      </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-      <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-      <c r="Z24">
-        <v>1</v>
-      </c>
-      <c r="AA24">
-        <v>1</v>
-      </c>
-      <c r="AB24">
-        <v>1</v>
-      </c>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AD24">
-        <v>1</v>
-      </c>
-      <c r="AE24">
-        <v>1</v>
-      </c>
-      <c r="AF24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.75">
-      <c r="A25" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:XFD25">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A5:XFD6">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3231,21 +3387,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3254,25 +3410,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A3,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A4,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B4)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3281,7 +3437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3290,7 +3446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3299,7 +3455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3308,7 +3464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3317,7 +3473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3326,7 +3482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -3335,7 +3491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3344,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3353,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -3362,7 +3518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3371,94 +3527,94 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A16,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B16)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A17,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A18,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B18)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A19,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B19)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A20,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B20)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A21,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B21)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A22,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B22)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A23,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B23)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A24,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B24)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25">
         <f>IFERROR(INDEX(Sheet1!$C$2:$AF$25,MATCH($A25,Sheet1!$A$2:$A$25,0),MATCH(About!$B$1,Sheet1!$C$1:$AF$1,0)),Sheet1!B25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3472,21 +3628,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3494,39 +3650,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3534,7 +3690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3542,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3550,15 +3706,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -3566,7 +3722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3574,7 +3730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3582,16 +3738,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
-        <f>B2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3599,81 +3754,81 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>27</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>28</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
       <c r="B18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>33</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
+      <c r="B20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>34</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>35</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A22" t="s">
+      <c r="B22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>36</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A23" t="s">
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A24" s="4" t="s">
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A25" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="B25">
         <v>1</v>
